--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484312_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484312_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5733</v>
+        <v>4.8734</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9661</v>
+        <v>2.0561</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6072</v>
+        <v>2.8174</v>
       </c>
       <c r="G2" t="n">
         <v>2.5237</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4049</v>
+        <v>1.7051</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7886</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6164</v>
+        <v>0.8265</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3321</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4353</v>
+        <v>4.1657</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5522</v>
+        <v>0.5004</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8832</v>
+        <v>3.6653</v>
       </c>
       <c r="G3" t="n">
         <v>4.1492</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0089</v>
+        <v>0.7393</v>
       </c>
       <c r="T3" t="n">
-        <v>1.728</v>
+        <v>0.6763</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2809</v>
+        <v>0.063</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3321</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0436</v>
+        <v>3.9329</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0358</v>
+        <v>1.1975</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0078</v>
+        <v>2.7354</v>
       </c>
       <c r="G4" t="n">
         <v>2.8583</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6849</v>
+        <v>0.5742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2337</v>
+        <v>-0.0721</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9187</v>
+        <v>0.6463</v>
       </c>
       <c r="V4" t="n">
         <v>0.1097</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3546</v>
+        <v>2.1983</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0397</v>
+        <v>-0.4301</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3942</v>
+        <v>2.6284</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1522</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>6.1889</v>
+        <v>2.5941</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0367</v>
+        <v>-1.6984</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3821</v>
+        <v>-0.9165</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6089</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2268</v>
+        <v>-1.4281</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2299</v>
+        <v>1.8122</v>
       </c>
       <c r="N5" t="n">
-        <v>0.58</v>
+        <v>2.0824</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8099</v>
+        <v>-0.2702</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9301</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4368</v>
+        <v>0.2125</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4758</v>
+        <v>0.4864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9126</v>
+        <v>-0.2739</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.2111</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.9925</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9826</v>
+        <v>1.9211</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4007</v>
+        <v>-0.2825</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3833</v>
+        <v>2.2036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8957000000000001</v>
+        <v>4.1522</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5941</v>
+        <v>6.1889</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6984</v>
+        <v>-2.0367</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9165</v>
+        <v>4.3821</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5116000000000001</v>
+        <v>5.6089</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4281</v>
+        <v>-1.2268</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8122</v>
+        <v>-0.2299</v>
       </c>
       <c r="N6" t="n">
-        <v>2.0824</v>
+        <v>0.58</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2702</v>
+        <v>-0.8099</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0032</v>
+        <v>0.0033</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4842</v>
+        <v>-0.7187</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.519</v>
+        <v>0.722</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>-3.2111</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.9925</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5606</v>
+        <v>1.4286</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.226</v>
+        <v>-0.9062</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7865</v>
+        <v>2.3348</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7846</v>
+        <v>2.3966</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6227</v>
+        <v>4.0689</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1619</v>
+        <v>-1.6723</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7586</v>
+        <v>1.3933</v>
       </c>
       <c r="K7" t="n">
-        <v>1.517</v>
+        <v>2.6605</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2416</v>
+        <v>-1.2673</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9741</v>
+        <v>1.0033</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1057</v>
+        <v>1.4083</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0797</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7581</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1255</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6845</v>
+        <v>-0.0145</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5969</v>
+        <v>0.0214</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0877</v>
+        <v>-0.0359</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5357</v>
+        <v>1.2348</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4723</v>
+        <v>0.1878</v>
       </c>
       <c r="F8" t="n">
-        <v>2.008</v>
+        <v>1.047</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3966</v>
+        <v>0.88</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0689</v>
+        <v>3.4285</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6723</v>
+        <v>-2.5486</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3933</v>
+        <v>1.3095</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6605</v>
+        <v>3.318</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2673</v>
+        <v>-2.0085</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0033</v>
+        <v>-0.4295</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4083</v>
+        <v>0.1105</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-0.5401</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9074</v>
+        <v>-0.4581</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5447</v>
+        <v>-0.4222</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3627</v>
+        <v>-0.0359</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0834</v>
+        <v>1.0896</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4189</v>
+        <v>-1.0237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5023</v>
+        <v>2.1134</v>
       </c>
       <c r="G9" t="n">
-        <v>0.88</v>
+        <v>1.7846</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4285</v>
+        <v>1.6227</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5486</v>
+        <v>0.1619</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3095</v>
+        <v>2.7586</v>
       </c>
       <c r="K9" t="n">
-        <v>3.318</v>
+        <v>1.517</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0085</v>
+        <v>1.2416</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4295</v>
+        <v>-0.9741</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1105</v>
+        <v>0.1057</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5401</v>
+        <v>-1.0797</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6095</v>
+        <v>-0.1555</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0289</v>
+        <v>-0.3946</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5806</v>
+        <v>0.2392</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4405</v>
+        <v>-0.4133</v>
       </c>
       <c r="E10" t="n">
         <v>-1.3322</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.9188</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5974</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1167</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U10" t="n">
-        <v>0.186</v>
+        <v>0.2132</v>
       </c>
       <c r="V10" t="n">
         <v>0.6642</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>20.1286</v>
+        <v>20.4311</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3356999999999999</v>
+        <v>-0.03289999999999993</v>
       </c>
       <c r="F11" t="n">
         <v>20.4641</v>
@@ -1312,13 +1312,13 @@
         <v>18.5575</v>
       </c>
       <c r="S11" t="n">
-        <v>2.214200000000001</v>
+        <v>2.5169</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1501999999999999</v>
+        <v>0.1524000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3646</v>
+        <v>2.3645</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1052</v>
@@ -1327,7 +1327,7 @@
         <v>1.2215</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3266</v>
+        <v>-3.326599999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.103</v>
+        <v>0.6907</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6238</v>
+        <v>0.3205</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4791</v>
+        <v>0.3702</v>
       </c>
       <c r="G12" t="n">
         <v>0.2678</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2575</v>
+        <v>-0.1548</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5339</v>
+        <v>0.2305</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2763</v>
+        <v>-0.3853</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3991</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.343</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9983</v>
+        <v>0.8882</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6553</v>
+        <v>-1.4925</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2954</v>
+        <v>-0.4433</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.9698</v>
+        <v>-1.6444</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6745</v>
+        <v>1.2011</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7198</v>
+        <v>1.7436</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0447</v>
+        <v>0.0025</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6751</v>
+        <v>1.741</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0152</v>
+        <v>-2.1868</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0146</v>
+        <v>-1.647</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.5399</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8194</v>
+        <v>-0.7573</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5693</v>
+        <v>-0.1326</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3887</v>
+        <v>-0.6246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3283</v>
+        <v>-0.5758</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X13" t="n">
-        <v>1.3283</v>
+        <v>-0.2437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4331</v>
+        <v>-0.7709</v>
       </c>
       <c r="E14" t="n">
-        <v>0.787</v>
+        <v>-2.0994</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2201</v>
+        <v>1.3284</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4433</v>
+        <v>-2.2954</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6444</v>
+        <v>-2.9698</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2011</v>
+        <v>0.6745</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7436</v>
+        <v>0.7198</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0025</v>
+        <v>0.0447</v>
       </c>
       <c r="L14" t="n">
-        <v>1.741</v>
+        <v>0.6751</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1868</v>
+        <v>-3.0152</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.647</v>
+        <v>-3.0146</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5399</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.586</v>
+        <v>0.3914</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2337</v>
+        <v>-0.6704</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3523</v>
+        <v>1.0619</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5758</v>
+        <v>1.3283</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2437</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8596</v>
+        <v>-1.4474</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.558</v>
+        <v>-1.2546</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3017</v>
+        <v>-0.1927</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3997</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1929</v>
+        <v>-0.7806</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.187</v>
+        <v>0.1164</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0059</v>
+        <v>-0.897</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2437</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8849</v>
+        <v>-1.7753</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4323</v>
+        <v>-1.5834</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4525</v>
+        <v>-0.1919</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1798</v>
+        <v>-1.9624</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8258</v>
+        <v>-1.9622</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6461</v>
+        <v>-0.0002</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.118</v>
+        <v>-1.3482</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2254</v>
+        <v>-1.3482</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1074</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0617</v>
+        <v>-0.6142</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6004</v>
+        <v>-0.614</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5387</v>
+        <v>-0.0002</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4017</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2392</v>
+        <v>-0.0399</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6409</v>
+        <v>0.0316</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6512</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8958</v>
+        <v>-2.021</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7856</v>
+        <v>-1.4323</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1102</v>
+        <v>-0.5887</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9624</v>
+        <v>-2.1798</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9622</v>
+        <v>-3.8258</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0002</v>
+        <v>1.6461</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3482</v>
+        <v>-0.118</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3482</v>
+        <v>-1.2254</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.1074</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6142</v>
+        <v>-2.0617</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.614</v>
+        <v>-2.6004</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0002</v>
+        <v>0.5387</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1288</v>
+        <v>0.2656</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>-0.2392</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1133</v>
+        <v>0.5047</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.6512</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9147</v>
+        <v>-2.074</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2997</v>
+        <v>-3.7042</v>
       </c>
       <c r="F18" t="n">
-        <v>1.385</v>
+        <v>1.6301</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2973</v>
@@ -1858,13 +1858,13 @@
         <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.59</v>
+        <v>0.4307</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1653</v>
+        <v>-0.2392</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4247</v>
+        <v>0.6698</v>
       </c>
       <c r="V18" t="n">
         <v>0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3248</v>
+        <v>-2.5349</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7351</v>
+        <v>-2.8362</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4103</v>
+        <v>0.3013</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0757</v>
@@ -1936,13 +1936,13 @@
         <v>2.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1778</v>
+        <v>-0.0322</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6491</v>
+        <v>-0.7502</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8269</v>
+        <v>0.7179</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2316</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0537</v>
+        <v>-2.5869</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7807</v>
+        <v>-2.4774</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.273</v>
+        <v>-0.1095</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3761</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1566</v>
+        <v>-0.6899</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.187</v>
+        <v>0.1164</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9696</v>
+        <v>-0.8062</v>
       </c>
       <c r="V20" t="n">
         <v>-0.521</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4776</v>
+        <v>-3.3959</v>
       </c>
       <c r="E21" t="n">
         <v>-3.2946</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.183</v>
+        <v>-0.1013</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4537</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.383</v>
+        <v>-0.3013</v>
       </c>
       <c r="T21" t="n">
         <v>-0.6052</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2223</v>
+        <v>0.304</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0444</v>
+        <v>-3.6087</v>
       </c>
       <c r="E22" t="n">
         <v>-2.9907</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0538</v>
+        <v>-0.618</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8272</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0134</v>
+        <v>-0.5777</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1511</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8623</v>
+        <v>-0.4266</v>
       </c>
       <c r="V22" t="n">
         <v>0.8195</v>
@@ -2206,10 +2206,10 @@
         <v>-20.1286</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.4642</v>
+        <v>-20.4641</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3353999999999999</v>
+        <v>0.3354</v>
       </c>
       <c r="G23" t="n">
         <v>-19.0428</v>
@@ -2254,7 +2254,7 @@
         <v>-2.3645</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1503999999999998</v>
+        <v>0.1502</v>
       </c>
       <c r="V23" t="n">
         <v>2.105</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484312_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484312_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.1089</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2348</v>
+        <v>1.0896</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1878</v>
+        <v>-1.0237</v>
       </c>
       <c r="F8" t="n">
-        <v>1.047</v>
+        <v>2.1134</v>
       </c>
       <c r="G8" t="n">
-        <v>0.88</v>
+        <v>1.7846</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4285</v>
+        <v>1.6227</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5486</v>
+        <v>0.1619</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3095</v>
+        <v>2.7586</v>
       </c>
       <c r="K8" t="n">
-        <v>3.318</v>
+        <v>1.517</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0085</v>
+        <v>1.2416</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4295</v>
+        <v>-0.9741</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1105</v>
+        <v>0.1057</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5401</v>
+        <v>-1.0797</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4581</v>
+        <v>-0.1555</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4222</v>
+        <v>-0.3946</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0359</v>
+        <v>0.2392</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0896</v>
+        <v>0.914</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0237</v>
+        <v>0.914</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1134</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7846</v>
+        <v>0.914</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6227</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1619</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7586</v>
+        <v>0.914</v>
       </c>
       <c r="K9" t="n">
-        <v>1.517</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2416</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9741</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0797</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1555</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3946</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2392</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4133</v>
+        <v>0.3208</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3322</v>
+        <v>-0.7261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9188</v>
+        <v>1.047</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5974</v>
+        <v>-0.034</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1773</v>
+        <v>3.1215</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5799</v>
+        <v>-3.1555</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0528</v>
+        <v>0.3955</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3073</v>
+        <v>3.011</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2544</v>
+        <v>-2.6155</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5445</v>
+        <v>-0.4295</v>
       </c>
       <c r="N10" t="n">
-        <v>0.13</v>
+        <v>0.1105</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6745</v>
+        <v>-0.5401</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.4581</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3026</v>
+        <v>-0.4222</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2132</v>
+        <v>-0.0359</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>20.4311</v>
+        <v>-0.4133</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03289999999999993</v>
+        <v>-1.3322</v>
       </c>
       <c r="F11" t="n">
-        <v>20.4641</v>
+        <v>0.9188</v>
       </c>
       <c r="G11" t="n">
-        <v>19.0429</v>
+        <v>-0.5974</v>
       </c>
       <c r="H11" t="n">
-        <v>26.4599</v>
+        <v>-1.1773</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.4171</v>
+        <v>0.5799</v>
       </c>
       <c r="J11" t="n">
-        <v>16.174</v>
+        <v>-0.0528</v>
       </c>
       <c r="K11" t="n">
-        <v>18.8653</v>
+        <v>-1.3073</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6915</v>
+        <v>1.2544</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8688</v>
+        <v>-0.5445</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5943</v>
+        <v>0.13</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.7256</v>
+        <v>-0.6745</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9766999999999999</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.5807</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>18.5575</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5169</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1524000000000001</v>
+        <v>-0.3026</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3645</v>
+        <v>0.2132</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1052</v>
+        <v>0.6642</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2215</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.326599999999999</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6907</v>
+        <v>20.4311</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3205</v>
+        <v>-0.03279999999999994</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3702</v>
+        <v>20.4641</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2678</v>
+        <v>19.0429</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4313</v>
+        <v>26.4599</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6992</v>
+        <v>-7.417</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0081</v>
+        <v>16.174</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2868</v>
+        <v>18.8653</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2949</v>
+        <v>-2.6915</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2597</v>
+        <v>2.8688</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1445</v>
+        <v>7.5943</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4043</v>
+        <v>-4.7256</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1953</v>
+        <v>-17.5807</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>18.5575</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1548</v>
+        <v>2.5169</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2305</v>
+        <v>0.1524</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3853</v>
+        <v>2.3645</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3991</v>
+        <v>-2.1052</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.2215</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6763</v>
-      </c>
+        <v>-3.3266</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6042999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8882</v>
+        <v>0.914</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4925</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4433</v>
+        <v>0.914</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6444</v>
+        <v>0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2011</v>
+        <v>0.607</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7436</v>
+        <v>0.914</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0025</v>
+        <v>0.307</v>
       </c>
       <c r="L13" t="n">
-        <v>1.741</v>
+        <v>0.607</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1868</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.647</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7573</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1326</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6246</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5758</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2437</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7709</v>
+        <v>0.6907</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0994</v>
+        <v>0.3205</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3284</v>
+        <v>0.3702</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2954</v>
+        <v>0.2678</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.9698</v>
+        <v>-1.4313</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6745</v>
+        <v>1.6992</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7198</v>
+        <v>0.0081</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0447</v>
+        <v>-1.2868</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6751</v>
+        <v>1.2949</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0152</v>
+        <v>0.2597</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0146</v>
+        <v>-0.1445</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4043</v>
       </c>
       <c r="P14" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-2.1488</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3914</v>
+        <v>-0.1548</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6704</v>
+        <v>0.2305</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0619</v>
+        <v>-0.3853</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3283</v>
+        <v>-0.3991</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>1.3283</v>
+        <v>-0.6763</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4474</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2546</v>
+        <v>0.8882</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1927</v>
+        <v>-1.4925</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3997</v>
+        <v>-0.4433</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0353</v>
+        <v>-1.6444</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3644</v>
+        <v>1.2011</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9802999999999999</v>
+        <v>1.7436</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3466</v>
+        <v>0.0025</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.741</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4194</v>
+        <v>-2.1868</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6887</v>
+        <v>-1.647</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2692</v>
+        <v>-0.5399</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.3907</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7806</v>
+        <v>-0.7573</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1164</v>
+        <v>-0.1326</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.897</v>
+        <v>-0.6246</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2437</v>
+        <v>-0.5758</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2437</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7753</v>
+        <v>-0.7709</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5834</v>
+        <v>-2.0994</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1919</v>
+        <v>1.3284</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9624</v>
+        <v>-2.2954</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9622</v>
+        <v>-2.9698</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0002</v>
+        <v>0.6745</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3482</v>
+        <v>0.7198</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3482</v>
+        <v>0.0447</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6751</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6142</v>
+        <v>-3.0152</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.614</v>
+        <v>-3.0146</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.3914</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0399</v>
+        <v>-0.6704</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0316</v>
+        <v>1.0619</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.021</v>
+        <v>-1.4474</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4323</v>
+        <v>-1.2546</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5887</v>
+        <v>-0.1927</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1798</v>
+        <v>-1.3997</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.8258</v>
+        <v>-1.0353</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6461</v>
+        <v>-0.3644</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.118</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2254</v>
+        <v>-0.3466</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1074</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0617</v>
+        <v>-0.4194</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6004</v>
+        <v>-0.6887</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5387</v>
+        <v>0.2692</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-0.3907</v>
       </c>
       <c r="R17" t="n">
         <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2656</v>
+        <v>-0.7806</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2392</v>
+        <v>0.1164</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5047</v>
+        <v>-0.897</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6512</v>
+        <v>-0.2437</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3991</v>
+        <v>-0.2437</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.074</v>
+        <v>-1.7753</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7042</v>
+        <v>-1.5834</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6301</v>
+        <v>-0.1919</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2973</v>
+        <v>-1.9624</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1443</v>
+        <v>-1.9622</v>
       </c>
       <c r="I18" t="n">
-        <v>1.847</v>
+        <v>-0.0002</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2494</v>
+        <v>-1.3482</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0182</v>
+        <v>-1.3482</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7688</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.048</v>
+        <v>-0.6142</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1261</v>
+        <v>-0.614</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0782</v>
+        <v>-0.0002</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.1022</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4307</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2392</v>
+        <v>-0.0399</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6698</v>
+        <v>0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5349</v>
+        <v>-2.021</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8362</v>
+        <v>-1.4323</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3013</v>
+        <v>-0.5887</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0757</v>
+        <v>-2.1798</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3582</v>
+        <v>-3.8258</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2825</v>
+        <v>1.6461</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1492</v>
+        <v>-0.118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8659</v>
+        <v>-1.2254</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2833</v>
+        <v>1.1074</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2249</v>
+        <v>-2.0617</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.2241</v>
+        <v>-2.6004</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0008</v>
+        <v>0.5387</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9301</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0322</v>
+        <v>0.2656</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7502</v>
+        <v>-0.2392</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7179</v>
+        <v>0.5047</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2316</v>
+        <v>1.6512</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1097</v>
+        <v>2.0503</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1219</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5869</v>
+        <v>-2.5349</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4774</v>
+        <v>-2.8362</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1095</v>
+        <v>0.3013</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3761</v>
+        <v>-2.0757</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8611</v>
+        <v>-2.3582</v>
       </c>
       <c r="I20" t="n">
-        <v>0.485</v>
+        <v>0.2825</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2263</v>
+        <v>1.1492</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3073</v>
+        <v>0.8659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0.2833</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1498</v>
+        <v>-3.2249</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5538</v>
+        <v>-3.2241</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4041</v>
+        <v>-0.0008</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3674</v>
+        <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6899</v>
+        <v>-0.0322</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1164</v>
+        <v>-0.7502</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8062</v>
+        <v>0.7179</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.521</v>
+        <v>-0.2316</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.521</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3959</v>
+        <v>-2.5869</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2946</v>
+        <v>-2.4774</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1013</v>
+        <v>-0.1095</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4537</v>
+        <v>-1.3761</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0895</v>
+        <v>-1.8611</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3642</v>
+        <v>0.485</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1236</v>
+        <v>-1.2263</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7572</v>
+        <v>-1.3073</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5773</v>
+        <v>-0.1498</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8468</v>
+        <v>-0.5538</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2694</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>-1.3674</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3013</v>
+        <v>-0.6899</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6052</v>
+        <v>0.1164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.304</v>
+        <v>-0.8062</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>-0.521</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.521</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6087</v>
+        <v>-2.988</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9907</v>
+        <v>-4.6181</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.618</v>
+        <v>1.6301</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8272</v>
+        <v>-2.2113</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.1377</v>
+        <v>-3.4513</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3105</v>
+        <v>1.24</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6908</v>
+        <v>-1.1633</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.7323</v>
+        <v>-1.3252</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0.1619</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1364</v>
+        <v>-1.048</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4055</v>
+        <v>-2.1261</v>
       </c>
       <c r="O22" t="n">
-        <v>0.269</v>
+        <v>1.0782</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3674</v>
+        <v>-4.1022</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5777</v>
+        <v>0.4307</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1511</v>
+        <v>-0.2392</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4266</v>
+        <v>0.6698</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8195</v>
+        <v>0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3991</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-3.3959</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.2946</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.1013</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.4537</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.0895</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.3642</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7572</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.5773</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.8468</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.3013</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.6052</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>J. MARTIN TRENADO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.6087</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.9907</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.618</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4.8272</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-5.1377</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-2.6908</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-2.7323</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.1364</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.4055</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.5777</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1511</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4266</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.3991</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484312_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-20.1286</v>
       </c>
-      <c r="E23" t="n">
-        <v>-20.4641</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.3354</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="E25" t="n">
+        <v>-20.464</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3354000000000003</v>
+      </c>
+      <c r="G25" t="n">
         <v>-19.0428</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>-26.4596</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>7.4171</v>
       </c>
-      <c r="J23" t="n">
-        <v>-2.8687</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J25" t="n">
+        <v>-2.8686</v>
+      </c>
+      <c r="K25" t="n">
         <v>-7.5945</v>
       </c>
-      <c r="L23" t="n">
-        <v>4.7257</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L25" t="n">
+        <v>4.725799999999999</v>
+      </c>
+      <c r="M25" t="n">
         <v>-16.174</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-18.8655</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>2.6914</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>-0.9767000000000002</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-18.5576</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>17.5808</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>-2.2143</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>-2.3645</v>
       </c>
-      <c r="U23" t="n">
-        <v>0.1502</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="U25" t="n">
+        <v>0.1501999999999998</v>
+      </c>
+      <c r="V25" t="n">
         <v>2.105</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W25" t="n">
         <v>3.3266</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-1.2216</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
